--- a/backend/data/financials_by_company/002471.SZ.xlsx
+++ b/backend/data/financials_by_company/002471.SZ.xlsx
@@ -4318,10 +4318,8 @@
           <t>Yixing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>214242</t>
-        </is>
+      <c r="D2" t="n">
+        <v>214242</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4538,7 +4536,7 @@
         <v>-7145991</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -4706,7 +4704,7 @@
         <v>1619089140</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>-1.5256</v>
